--- a/TPR.xlsx
+++ b/TPR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D3CF28-CF98-40A1-AD12-17BF4276B3D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC385A01-3CD8-448A-B635-8BFC23DBD49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{FE2400EE-DFF5-46AE-8520-2B6C3CEB7AD1}"/>
   </bookViews>
@@ -348,7 +348,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -382,6 +382,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -752,7 +753,7 @@
         <v>4</v>
       </c>
       <c r="J2" s="2">
-        <v>154.69999999999999</v>
+        <v>134.28</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -760,10 +761,10 @@
         <v>5</v>
       </c>
       <c r="J3" s="3">
-        <v>202.464223</v>
+        <v>202.044714</v>
       </c>
       <c r="K3" s="20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -775,7 +776,7 @@
       </c>
       <c r="J4" s="3">
         <f>+J2*J3</f>
-        <v>31321.2152981</v>
+        <v>27130.56419592</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -786,11 +787,11 @@
         <v>7</v>
       </c>
       <c r="J5" s="3">
-        <f>1053.3+24.4</f>
-        <v>1077.7</v>
+        <f>1046.5+0.0221</f>
+        <v>1046.5220999999999</v>
       </c>
       <c r="K5" s="20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -798,11 +799,10 @@
         <v>8</v>
       </c>
       <c r="J6" s="3">
-        <f>2379.3+17.1</f>
-        <v>2396.4</v>
+        <v>2377.1</v>
       </c>
       <c r="K6" s="20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -814,7 +814,7 @@
       </c>
       <c r="J7" s="3">
         <f>+J4-J5+J6</f>
-        <v>32639.915298100001</v>
+        <v>28461.14209592</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -1186,7 +1186,9 @@
       <c r="L10" s="13">
         <v>2142.4</v>
       </c>
-      <c r="M10" s="13"/>
+      <c r="M10" s="13">
+        <v>1701</v>
+      </c>
       <c r="N10" s="13"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
@@ -1380,7 +1382,9 @@
       <c r="L11" s="13">
         <v>360</v>
       </c>
-      <c r="M11" s="13"/>
+      <c r="M11" s="13">
+        <v>219.6</v>
+      </c>
       <c r="N11" s="13"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
@@ -1574,7 +1578,9 @@
       <c r="L12" s="13">
         <v>0</v>
       </c>
-      <c r="M12" s="13"/>
+      <c r="M12" s="21">
+        <v>0</v>
+      </c>
       <c r="N12" s="13"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -1768,7 +1774,9 @@
       <c r="L13" s="14">
         <v>2502.4</v>
       </c>
-      <c r="M13" s="14"/>
+      <c r="M13" s="14">
+        <v>1920.6</v>
+      </c>
       <c r="N13" s="14"/>
       <c r="O13" s="3"/>
       <c r="P13" s="15"/>
@@ -1962,7 +1970,9 @@
       <c r="L14" s="13">
         <v>614</v>
       </c>
-      <c r="M14" s="13"/>
+      <c r="M14" s="13">
+        <v>444.1</v>
+      </c>
       <c r="N14" s="13"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -2164,7 +2174,10 @@
         <f t="shared" si="4"/>
         <v>1888.4</v>
       </c>
-      <c r="M15" s="13"/>
+      <c r="M15" s="13">
+        <f t="shared" si="4"/>
+        <v>1476.5</v>
+      </c>
       <c r="N15" s="13"/>
       <c r="O15" s="3"/>
       <c r="P15" s="13">
@@ -2373,7 +2386,9 @@
       <c r="L16" s="13">
         <v>1172</v>
       </c>
-      <c r="M16" s="13"/>
+      <c r="M16" s="13">
+        <v>1049</v>
+      </c>
       <c r="N16" s="13"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
@@ -2576,7 +2591,10 @@
         <f t="shared" si="6"/>
         <v>716.40000000000009</v>
       </c>
-      <c r="M17" s="13"/>
+      <c r="M17" s="13">
+        <f t="shared" si="6"/>
+        <v>427.5</v>
+      </c>
       <c r="N17" s="13"/>
       <c r="O17" s="3"/>
       <c r="P17" s="13">
@@ -2786,7 +2804,9 @@
       <c r="L18" s="13">
         <v>17.399999999999999</v>
       </c>
-      <c r="M18" s="13"/>
+      <c r="M18" s="13">
+        <v>13.1</v>
+      </c>
       <c r="N18" s="13"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
@@ -2981,7 +3001,9 @@
       <c r="L19" s="13">
         <v>1.9</v>
       </c>
-      <c r="M19" s="13"/>
+      <c r="M19" s="13">
+        <v>-1.6</v>
+      </c>
       <c r="N19" s="13"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
@@ -3183,7 +3205,10 @@
         <f t="shared" si="8"/>
         <v>697.10000000000014</v>
       </c>
-      <c r="M20" s="13"/>
+      <c r="M20" s="13">
+        <f t="shared" si="8"/>
+        <v>416</v>
+      </c>
       <c r="N20" s="13"/>
       <c r="O20" s="3"/>
       <c r="P20" s="13">
@@ -3392,7 +3417,9 @@
       <c r="L21" s="13">
         <v>135.80000000000001</v>
       </c>
-      <c r="M21" s="13"/>
+      <c r="M21" s="13">
+        <v>72.2</v>
+      </c>
       <c r="N21" s="13"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
@@ -3594,7 +3621,10 @@
         <f t="shared" si="10"/>
         <v>561.30000000000018</v>
       </c>
-      <c r="M22" s="13"/>
+      <c r="M22" s="13">
+        <f t="shared" si="10"/>
+        <v>343.8</v>
+      </c>
       <c r="N22" s="13"/>
       <c r="O22" s="3"/>
       <c r="P22" s="13">
@@ -3955,7 +3985,7 @@
         <v>0.80604751619870452</v>
       </c>
       <c r="H24" s="19">
-        <f t="shared" ref="H24:L24" si="12">+H22/H25</f>
+        <f t="shared" ref="H24:M24" si="12">+H22/H25</f>
         <v>1.4115507048658491</v>
       </c>
       <c r="I24" s="19">
@@ -3974,7 +4004,10 @@
         <f t="shared" si="12"/>
         <v>2.7501224889759932</v>
       </c>
-      <c r="M24" s="19"/>
+      <c r="M24" s="19">
+        <f t="shared" si="12"/>
+        <v>1.6977777777777778</v>
+      </c>
       <c r="N24" s="19"/>
       <c r="O24" s="19"/>
       <c r="P24" s="19" t="e">
@@ -4183,7 +4216,9 @@
       <c r="L25" s="3">
         <v>204.1</v>
       </c>
-      <c r="M25" s="3"/>
+      <c r="M25" s="3">
+        <v>202.5</v>
+      </c>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
@@ -4720,7 +4755,10 @@
         <f>+L10/H10-1</f>
         <v>0.25337857602527358</v>
       </c>
-      <c r="M28" s="16"/>
+      <c r="M28" s="16">
+        <f>+M10/I10-1</f>
+        <v>0.31503672207189792</v>
+      </c>
       <c r="N28" s="16"/>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
@@ -4907,7 +4945,7 @@
         <v>-9.5569070373588194E-2</v>
       </c>
       <c r="I29" s="16">
-        <f t="shared" ref="I29:L31" si="17">+I11/E11-1</f>
+        <f t="shared" ref="I29:M31" si="17">+I11/E11-1</f>
         <v>-0.12753829711435694</v>
       </c>
       <c r="J29" s="16">
@@ -4922,7 +4960,10 @@
         <f t="shared" si="17"/>
         <v>-0.13544668587896247</v>
       </c>
-      <c r="M29" s="16"/>
+      <c r="M29" s="16">
+        <f t="shared" si="17"/>
+        <v>-0.10330747243772975</v>
+      </c>
       <c r="N29" s="16"/>
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
@@ -5124,7 +5165,10 @@
         <f t="shared" si="17"/>
         <v>-1</v>
       </c>
-      <c r="M30" s="16"/>
+      <c r="M30" s="16">
+        <f t="shared" si="17"/>
+        <v>-1</v>
+      </c>
       <c r="N30" s="16"/>
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
@@ -5326,7 +5370,10 @@
         <f t="shared" si="17"/>
         <v>0.13983784276213895</v>
       </c>
-      <c r="M31" s="17"/>
+      <c r="M31" s="17">
+        <f t="shared" si="17"/>
+        <v>0.21204089360090883</v>
+      </c>
       <c r="N31" s="17"/>
       <c r="O31" s="15"/>
       <c r="P31" s="3"/>
@@ -5540,7 +5587,10 @@
         <f>+L15/L13</f>
         <v>0.75463554987212278</v>
       </c>
-      <c r="M32" s="16"/>
+      <c r="M32" s="16">
+        <f>+M15/M13</f>
+        <v>0.76877017598667086</v>
+      </c>
       <c r="N32" s="16"/>
       <c r="O32" s="3"/>
       <c r="P32" s="16" t="e">
@@ -5757,7 +5807,10 @@
         <f>+L17/L13</f>
         <v>0.28628516624040923</v>
       </c>
-      <c r="M33" s="16"/>
+      <c r="M33" s="16">
+        <f>+M17/M13</f>
+        <v>0.22258669165885661</v>
+      </c>
       <c r="N33" s="16"/>
       <c r="O33" s="3"/>
       <c r="P33" s="16" t="e">
@@ -5974,7 +6027,10 @@
         <f>+L21/L20</f>
         <v>0.19480705781093097</v>
       </c>
-      <c r="M34" s="16"/>
+      <c r="M34" s="16">
+        <f>+M21/M20</f>
+        <v>0.1735576923076923</v>
+      </c>
       <c r="N34" s="16"/>
       <c r="O34" s="3"/>
       <c r="P34" s="16" t="e">
